--- a/engine_package/Res/MuScriptEditor/天使之战_v1.0.0.0/cfg_ui.xlsx
+++ b/engine_package/Res/MuScriptEditor/天使之战_v1.0.0.0/cfg_ui.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -831,6 +831,12 @@
   </si>
   <si>
     <t>456</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>Equip/Panel</t>
   </si>
 </sst>
 </file>
@@ -876,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1968,6 +1974,17 @@
         <v>272</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
